--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104573_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104573_W13.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0064</v>
+        <v>9.087400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>11.345</v>
+        <v>10.3718</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3386</v>
+        <v>-1.2844</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4857</v>
+        <v>5.4878</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="I2" t="n">
-        <v>4.542</v>
+        <v>4.5403</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6814</v>
+        <v>6.6624</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9048</v>
+        <v>1.8961</v>
       </c>
       <c r="L2" t="n">
-        <v>4.7765</v>
+        <v>4.7663</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1957</v>
+        <v>-1.1745</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3354</v>
+        <v>-0.5794</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2249</v>
+        <v>0.2832</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8895</v>
+        <v>-0.8626</v>
       </c>
       <c r="V2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9019</v>
+        <v>3.1117</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0321</v>
+        <v>4.2039</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1302</v>
+        <v>-1.0922</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7993</v>
+        <v>4.7828</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9235</v>
+        <v>-0.9247</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7228</v>
+        <v>5.7075</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9649</v>
+        <v>5.9149</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6367</v>
+        <v>0.613</v>
       </c>
       <c r="L3" t="n">
-        <v>5.3282</v>
+        <v>5.3019</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1656</v>
+        <v>-1.1321</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5602</v>
+        <v>-1.5378</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6291</v>
+        <v>-0.3948</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1693</v>
+        <v>0.0692</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4597</v>
+        <v>-0.464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0008</v>
+        <v>2.0823</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1669</v>
+        <v>2.2083</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1661</v>
+        <v>-0.126</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7461</v>
+        <v>1.7506</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0393</v>
+        <v>-1.0179</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7853</v>
+        <v>2.7684</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2667</v>
+        <v>2.2365</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1905</v>
+        <v>0.1896</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0762</v>
+        <v>2.0469</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5206</v>
+        <v>-0.486</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2298</v>
+        <v>-1.2075</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7168</v>
+        <v>-0.6502</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0998</v>
+        <v>-0.0283</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.617</v>
+        <v>-0.622</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.706</v>
+        <v>1.2865</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1127</v>
+        <v>0.9115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5933</v>
+        <v>0.375</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4748</v>
+        <v>-0.4766</v>
       </c>
       <c r="H5" t="n">
-        <v>0.57</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0449</v>
+        <v>-1.0426</v>
       </c>
       <c r="J5" t="n">
-        <v>1.254</v>
+        <v>1.2254</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8863</v>
+        <v>0.8683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3678</v>
+        <v>0.357</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7289</v>
+        <v>-1.702</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1809</v>
+        <v>-0.2369</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0998</v>
+        <v>-0.2652</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2806</v>
+        <v>0.0283</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0171</v>
+        <v>-0.3239</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0405</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0576</v>
+        <v>-0.3978</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.6852</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3753</v>
+        <v>-0.368</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3198</v>
+        <v>-0.3172</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1466</v>
+        <v>0.1462</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8417</v>
+        <v>-0.8314</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2586</v>
+        <v>-0.094</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.1361</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6741</v>
+        <v>-0.4611</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7268</v>
+        <v>-1.6155</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0527</v>
+        <v>1.1543</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2781</v>
+        <v>-1.2799</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1587</v>
+        <v>0.1607</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4368</v>
+        <v>-1.4406</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5181</v>
+        <v>-1.5248</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M7" t="n">
-        <v>0.24</v>
+        <v>0.2449</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3033</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2292</v>
+        <v>-1.0388</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2541</v>
+        <v>-3.2191</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0249</v>
+        <v>2.1803</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9055</v>
+        <v>-1.9123</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2697</v>
+        <v>0.2781</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1752</v>
+        <v>-2.1904</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1411</v>
+        <v>-2.1735</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.0416</v>
+        <v>-3.0699</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2356</v>
+        <v>0.2613</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2311</v>
+        <v>-0.037</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0212</v>
+        <v>0.0926</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2523</v>
+        <v>-0.1297</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1966</v>
+        <v>-2.0947</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9644</v>
+        <v>-2.1043</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2323</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6908</v>
+        <v>0.7009</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1283</v>
+        <v>0.1346</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5625</v>
+        <v>0.5662</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7034</v>
+        <v>0.7005</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5541</v>
+        <v>0.5516</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0126</v>
+        <v>0.0003</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0614</v>
+        <v>0.1637</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2299</v>
+        <v>0.1136</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1685</v>
+        <v>0.0501</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5195</v>
+        <v>-2.7355</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5111</v>
+        <v>0.3544</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0306</v>
+        <v>-3.0899</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8922</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.398</v>
+        <v>0.4128</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2902</v>
+        <v>-1.2994</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5184</v>
+        <v>1.4917</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0638</v>
+        <v>0.0438</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4106</v>
+        <v>-2.3783</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0566</v>
+        <v>-1.0351</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8127</v>
+        <v>-1.0279</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.378</v>
+        <v>-0.4952</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4346</v>
+        <v>-0.5326</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1858</v>
+        <v>-3.8213</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7167</v>
+        <v>-2.491</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4691</v>
+        <v>-1.3303</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.991</v>
+        <v>-3.9885</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5094</v>
+        <v>-1.5052</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4816</v>
+        <v>-2.4833</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2298</v>
+        <v>-2.24</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7612</v>
+        <v>-1.7485</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8753</v>
+        <v>-0.5157</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3883</v>
+        <v>-0.2647</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3261</v>
+        <v>-3.93</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4268</v>
+        <v>-1.1267</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8993</v>
+        <v>-2.8032</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5067</v>
+        <v>-0.4919</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2105</v>
+        <v>-0.1991</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4544</v>
+        <v>0.453</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1716</v>
+        <v>-1.1441</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3556</v>
+        <v>-0.9917</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.747</v>
+        <v>-0.4416</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6085</v>
+        <v>-0.5501</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9601</v>
+        <v>-4.2795</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2233</v>
+        <v>-4.7279</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2631</v>
+        <v>0.4484</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3902</v>
+        <v>-0.3938</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1456</v>
+        <v>0.1519</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5359</v>
+        <v>-0.5456</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5655</v>
+        <v>0.5359</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.1051</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9557</v>
+        <v>-0.9296</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3262</v>
+        <v>-0.6306</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2521</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0741</v>
+        <v>0.0805</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.459200000000002</v>
+        <v>-3.116899999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>2.815200000000001</v>
+        <v>2.839300000000005</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.2746</v>
+        <v>-5.9562</v>
       </c>
       <c r="G14" t="n">
-        <v>2.377800000000001</v>
+        <v>2.408199999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7403</v>
+        <v>-1.656</v>
       </c>
       <c r="I14" t="n">
-        <v>4.117699999999999</v>
+        <v>4.0642</v>
       </c>
       <c r="J14" t="n">
-        <v>13.6663</v>
+        <v>13.4282</v>
       </c>
       <c r="K14" t="n">
-        <v>6.6172</v>
+        <v>6.5382</v>
       </c>
       <c r="L14" t="n">
-        <v>7.049000000000001</v>
+        <v>6.8898</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.2886</v>
+        <v>-11.02</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.3574</v>
+        <v>-8.1943</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.9313</v>
+        <v>-2.8256</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.5368</v>
+        <v>-4.5528</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.1468</v>
+        <v>-18.2106</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6098</v>
+        <v>13.6578</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.4138</v>
+        <v>-5.0863</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3134</v>
+        <v>-1.9547</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.100200000000001</v>
+        <v>-3.1318</v>
       </c>
       <c r="V14" t="n">
-        <v>4.1134</v>
+        <v>4.1137</v>
       </c>
       <c r="W14" t="n">
-        <v>9.6091</v>
+        <v>9.5761</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.495699999999999</v>
+        <v>-5.462400000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.0643</v>
+        <v>9.160500000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>11.6171</v>
+        <v>9.6799</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5528</v>
+        <v>-0.5194</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1587</v>
+        <v>4.155</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1719</v>
+        <v>4.1513</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0132</v>
+        <v>0.0037</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3462</v>
+        <v>6.3135</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9282</v>
+        <v>4.8985</v>
       </c>
       <c r="L15" t="n">
-        <v>1.418</v>
+        <v>1.415</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1875</v>
+        <v>-2.1585</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4312</v>
+        <v>-1.4113</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>3.894</v>
+        <v>2.0149</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3934</v>
+        <v>1.514</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="V15" t="n">
-        <v>4.1458</v>
+        <v>4.1287</v>
       </c>
       <c r="W15" t="n">
-        <v>4.1458</v>
+        <v>4.1287</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6641</v>
+        <v>5.0235</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3801</v>
+        <v>1.8362</v>
       </c>
       <c r="F16" t="n">
-        <v>3.284</v>
+        <v>3.1874</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2786</v>
+        <v>3.2811</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0187</v>
+        <v>-0.02</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2973</v>
+        <v>3.3012</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1453</v>
+        <v>2.1291</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1283</v>
+        <v>-0.1346</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2736</v>
+        <v>2.2638</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1333</v>
+        <v>1.152</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0237</v>
+        <v>1.0374</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2265</v>
+        <v>0.575</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5383</v>
+        <v>-0.0653</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7649</v>
+        <v>0.6404</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7648</v>
+        <v>3.4584</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8986</v>
+        <v>2.6818</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8661</v>
+        <v>0.7765</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0167</v>
+        <v>2.9937</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.8609</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8649</v>
+        <v>3.8547</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6456</v>
+        <v>2.6009</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6274</v>
+        <v>-0.6452</v>
       </c>
       <c r="L17" t="n">
-        <v>3.273</v>
+        <v>3.2462</v>
       </c>
       <c r="M17" t="n">
-        <v>0.371</v>
+        <v>0.3928</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5919</v>
+        <v>0.6085</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0012</v>
+        <v>0.7039</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5202</v>
+        <v>0.3085</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5214</v>
+        <v>0.3953</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.2946</v>
+        <v>-2.2879</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2946</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4444</v>
+        <v>0.3164</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5621</v>
+        <v>-1.7515</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1177</v>
+        <v>2.0679</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1881</v>
+        <v>1.0841</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3117</v>
+        <v>1.3384</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8764</v>
+        <v>-0.2543</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5775</v>
+        <v>0.6204</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8068</v>
+        <v>1.2238</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2293</v>
+        <v>-0.6035</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7656</v>
+        <v>0.4638</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1185</v>
+        <v>0.1146</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6471</v>
+        <v>0.3492</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5878</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3277</v>
+        <v>0.0046</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1584</v>
+        <v>-0.0955</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1693</v>
+        <v>0.1002</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3048</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1093</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1322</v>
+        <v>0.1386</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8776</v>
+        <v>1.0606</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7454</v>
+        <v>-0.922</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2465</v>
+        <v>-2.1747</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4937</v>
+        <v>-0.3103</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7401</v>
+        <v>-1.8645</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4421</v>
+        <v>0.5574</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7304</v>
+        <v>0.7961</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.1725</v>
+        <v>-0.2388</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8044</v>
+        <v>-2.7321</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2368</v>
+        <v>-1.1064</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5676</v>
+        <v>-1.6257</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7779</v>
+        <v>1.0173</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3357</v>
+        <v>0.6917</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4422</v>
+        <v>0.3256</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9320000000000001</v>
+        <v>1.2961</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7712</v>
+        <v>1.405</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6427</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0892</v>
+        <v>-1.7863</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4465</v>
+        <v>1.7139</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0753</v>
+        <v>-2.2532</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3391</v>
+        <v>0.4831</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2638</v>
+        <v>-2.7363</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6297</v>
+        <v>-1.4695</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2295</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5998</v>
+        <v>-2.1827</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4455</v>
+        <v>-0.7836</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1096</v>
+        <v>-0.2301</v>
       </c>
       <c r="O20" t="n">
-        <v>0.336</v>
+        <v>-0.5535</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>2.2763</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9448</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4506</v>
+        <v>0.4572</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4942</v>
+        <v>0.379</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5463</v>
+        <v>-0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.679</v>
+        <v>-0.9342</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1649</v>
+        <v>1.0312</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8439</v>
+        <v>-1.9654</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0846</v>
+        <v>-2.077</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1255</v>
+        <v>-0.129</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9591</v>
+        <v>-1.9479</v>
       </c>
       <c r="J21" t="n">
-        <v>1.177</v>
+        <v>1.1594</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2917</v>
+        <v>1.2788</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.2615</v>
+        <v>-3.2364</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4171</v>
+        <v>-1.4078</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8444</v>
+        <v>-1.8285</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7516</v>
+        <v>0.4795</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2148</v>
+        <v>0.0994</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.3801</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2973</v>
+        <v>-2.3108</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9792</v>
+        <v>0.8441</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2765</v>
+        <v>-3.1549</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4327</v>
+        <v>-1.4337</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3319</v>
+        <v>0.3331</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7646</v>
+        <v>-1.7668</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6616</v>
+        <v>0.6423</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2295</v>
+        <v>1.2238</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0944</v>
+        <v>-2.0759</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6403</v>
+        <v>0.6189</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5444</v>
+        <v>0.4294</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0959</v>
+        <v>0.1895</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2657</v>
+        <v>-2.9904</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7658</v>
+        <v>-0.5322</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4999</v>
+        <v>-2.4582</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6657</v>
+        <v>-1.6639</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4849</v>
+        <v>-0.4826</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1808</v>
+        <v>-1.1813</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7144</v>
+        <v>-0.7179</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9513</v>
+        <v>-0.946</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1878</v>
+        <v>0.0801</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0514</v>
+        <v>0.1857</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8443</v>
+        <v>-3.1572</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1964</v>
+        <v>-1.7973</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6479</v>
+        <v>-1.3599</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.0691</v>
+        <v>-4.1025</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3125</v>
+        <v>-2.3447</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7566</v>
+        <v>-1.7578</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6744</v>
+        <v>-0.7387</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.0368</v>
+        <v>-1.0804</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3623</v>
+        <v>0.3417</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.3947</v>
+        <v>-3.3638</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1189</v>
+        <v>-2.0995</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5997</v>
+        <v>0.1242</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6412</v>
+        <v>-0.1677</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0414</v>
+        <v>0.2919</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5978</v>
+        <v>0.5936</v>
       </c>
       <c r="W24" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6171</v>
+        <v>-4.3773</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3986</v>
+        <v>-5.3105</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7814</v>
+        <v>0.9332</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2202</v>
+        <v>-0.2172</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4948</v>
+        <v>-0.5022</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2746</v>
+        <v>0.285</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0635</v>
+        <v>-0.0769</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1008</v>
+        <v>-0.1142</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1567</v>
+        <v>-0.1403</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.9903</v>
+        <v>-5.0079</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.473</v>
+        <v>-0.2301</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3448</v>
+        <v>-0.2257</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1282</v>
+        <v>-0.0044</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.4593</v>
+        <v>4.255100000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>6.2744</v>
+        <v>5.956</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.8153</v>
+        <v>-1.700900000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.3776</v>
+        <v>-2.408300000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7402</v>
+        <v>1.656200000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.1178</v>
+        <v>-4.064300000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>11.2885</v>
+        <v>11.02</v>
       </c>
       <c r="K26" t="n">
-        <v>8.3574</v>
+        <v>8.194300000000002</v>
       </c>
       <c r="L26" t="n">
-        <v>2.931</v>
+        <v>2.8255</v>
       </c>
       <c r="M26" t="n">
-        <v>-13.6663</v>
+        <v>-13.428</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.617300000000001</v>
+        <v>-6.5382</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.0488</v>
+        <v>-6.889799999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>4.5366</v>
+        <v>4.552599999999998</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.6097</v>
+        <v>-13.6577</v>
       </c>
       <c r="R26" t="n">
-        <v>18.1465</v>
+        <v>18.2105</v>
       </c>
       <c r="S26" t="n">
-        <v>5.4139</v>
+        <v>6.2245</v>
       </c>
       <c r="T26" t="n">
-        <v>3.100200000000001</v>
+        <v>3.1317</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3136</v>
+        <v>3.0929</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.113399999999999</v>
+        <v>-4.1136</v>
       </c>
       <c r="W26" t="n">
-        <v>5.4958</v>
+        <v>5.4623</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.6091</v>
+        <v>-9.575900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104573_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104573_W13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-5.462400000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104573_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-9.575900000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
